--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/4.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/4.xlsx
@@ -426,13 +426,13 @@
         <v>-2.751112796940141</v>
       </c>
       <c r="E2">
-        <v>-10.39014959782233</v>
+        <v>-14.43945588172631</v>
       </c>
       <c r="F2">
-        <v>-3.518769850453151</v>
+        <v>-4.95142630339048</v>
       </c>
       <c r="G2">
-        <v>-7.984891297646942</v>
+        <v>-10.48436856503157</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.534275967732755</v>
       </c>
       <c r="E3">
-        <v>-12.13010840987998</v>
+        <v>-15.59118291421452</v>
       </c>
       <c r="F3">
-        <v>-2.707206708786837</v>
+        <v>-5.188084243431076</v>
       </c>
       <c r="G3">
-        <v>-7.835388314009135</v>
+        <v>-9.987593473489943</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.271647120266174</v>
       </c>
       <c r="E4">
-        <v>-11.76667334647821</v>
+        <v>-16.27231787790905</v>
       </c>
       <c r="F4">
-        <v>-2.694047264225964</v>
+        <v>-4.88132819703078</v>
       </c>
       <c r="G4">
-        <v>-8.170097518940519</v>
+        <v>-10.15182366736622</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.842137771261497</v>
       </c>
       <c r="E5">
-        <v>-11.42523369025272</v>
+        <v>-16.32716933987606</v>
       </c>
       <c r="F5">
-        <v>-2.749327534484386</v>
+        <v>-5.08397668498204</v>
       </c>
       <c r="G5">
-        <v>-8.476264758629556</v>
+        <v>-11.05498856733284</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.230642573201529</v>
       </c>
       <c r="E6">
-        <v>-13.39260574161268</v>
+        <v>-15.8750964403798</v>
       </c>
       <c r="F6">
-        <v>-2.512981060587242</v>
+        <v>-4.644305775332952</v>
       </c>
       <c r="G6">
-        <v>-8.676511479512536</v>
+        <v>-11.01213450024201</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.398799205744319</v>
       </c>
       <c r="E7">
-        <v>-13.37046497204002</v>
+        <v>-17.24241251952852</v>
       </c>
       <c r="F7">
-        <v>-2.961860930653252</v>
+        <v>-4.718091773369915</v>
       </c>
       <c r="G7">
-        <v>-9.331932382250049</v>
+        <v>-10.87968490027335</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.340924350434848</v>
       </c>
       <c r="E8">
-        <v>-13.99439360294636</v>
+        <v>-16.87222018130126</v>
       </c>
       <c r="F8">
-        <v>-2.581616270113598</v>
+        <v>-4.683067571212149</v>
       </c>
       <c r="G8">
-        <v>-9.046010161492799</v>
+        <v>-11.45853788564269</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.056113974191741</v>
       </c>
       <c r="E9">
-        <v>-13.58136919632614</v>
+        <v>-17.60386650112835</v>
       </c>
       <c r="F9">
-        <v>-3.354021656282177</v>
+        <v>-4.546998284893497</v>
       </c>
       <c r="G9">
-        <v>-8.660237403103832</v>
+        <v>-11.27304970393328</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.566419770017864</v>
       </c>
       <c r="E10">
-        <v>-15.27569252234657</v>
+        <v>-18.39136520685174</v>
       </c>
       <c r="F10">
-        <v>-2.564908099599132</v>
+        <v>-4.572376148645662</v>
       </c>
       <c r="G10">
-        <v>-8.50903482473721</v>
+        <v>-10.73954013062239</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.910682931329153</v>
       </c>
       <c r="E11">
-        <v>-16.59502239784823</v>
+        <v>-18.76058154041767</v>
       </c>
       <c r="F11">
-        <v>-2.468997236600797</v>
+        <v>-4.462218194686578</v>
       </c>
       <c r="G11">
-        <v>-7.435477068286994</v>
+        <v>-10.94384525397226</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.145177366658749</v>
       </c>
       <c r="E12">
-        <v>-15.20240080209732</v>
+        <v>-18.48499104974735</v>
       </c>
       <c r="F12">
-        <v>-2.338827582924882</v>
+        <v>-4.56809100407098</v>
       </c>
       <c r="G12">
-        <v>-7.232324588674104</v>
+        <v>-9.905458143281225</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.332684930731551</v>
       </c>
       <c r="E13">
-        <v>-15.88169173996362</v>
+        <v>-19.37183872357196</v>
       </c>
       <c r="F13">
-        <v>-2.526819766418411</v>
+        <v>-4.341561512264414</v>
       </c>
       <c r="G13">
-        <v>-7.499949405964536</v>
+        <v>-9.424838339269405</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.5454833658811</v>
       </c>
       <c r="E14">
-        <v>-16.49959406123764</v>
+        <v>-20.29170858064029</v>
       </c>
       <c r="F14">
-        <v>-2.675145576828884</v>
+        <v>-4.192067703815992</v>
       </c>
       <c r="G14">
-        <v>-6.024372227534854</v>
+        <v>-8.713765499455427</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8456962687754095</v>
       </c>
       <c r="E15">
-        <v>-16.05023320873649</v>
+        <v>-20.42781762217757</v>
       </c>
       <c r="F15">
-        <v>-1.795674532215872</v>
+        <v>-4.115172842916323</v>
       </c>
       <c r="G15">
-        <v>-5.746539398893169</v>
+        <v>-7.676207300172071</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.288807555399307</v>
       </c>
       <c r="E16">
-        <v>-17.21975259854026</v>
+        <v>-21.33023153204764</v>
       </c>
       <c r="F16">
-        <v>-1.671748283654857</v>
+        <v>-3.792765622807532</v>
       </c>
       <c r="G16">
-        <v>-4.957334805700942</v>
+        <v>-7.491239962008581</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.08314313667567402</v>
       </c>
       <c r="E17">
-        <v>-18.6086155380422</v>
+        <v>-22.05057696385987</v>
       </c>
       <c r="F17">
-        <v>-1.902295357365002</v>
+        <v>-3.480726249112181</v>
       </c>
       <c r="G17">
-        <v>-5.908214979187041</v>
+        <v>-6.84172064741928</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.2528374086724323</v>
       </c>
       <c r="E18">
-        <v>-19.83250046408797</v>
+        <v>-22.14909113648481</v>
       </c>
       <c r="F18">
-        <v>-1.38008260623136</v>
+        <v>-3.052421368596905</v>
       </c>
       <c r="G18">
-        <v>-4.63241719835853</v>
+        <v>-6.818208281631715</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2133677501956207</v>
       </c>
       <c r="E19">
-        <v>-20.11753535731095</v>
+        <v>-23.08390840111119</v>
       </c>
       <c r="F19">
-        <v>-0.7838502574531652</v>
+        <v>-2.778225959698449</v>
       </c>
       <c r="G19">
-        <v>-3.88820617744955</v>
+        <v>-6.25955332179152</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.01847644640671301</v>
       </c>
       <c r="E20">
-        <v>-21.90494460875476</v>
+        <v>-23.67545859652917</v>
       </c>
       <c r="F20">
-        <v>-0.5729330060871606</v>
+        <v>-2.741400886806997</v>
       </c>
       <c r="G20">
-        <v>-3.817444556052015</v>
+        <v>-6.557559373888737</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.4095149853530295</v>
       </c>
       <c r="E21">
-        <v>-21.49208633058753</v>
+        <v>-25.09282087214208</v>
       </c>
       <c r="F21">
-        <v>-0.5832105604536941</v>
+        <v>-1.78798065577867</v>
       </c>
       <c r="G21">
-        <v>-3.803845187476906</v>
+        <v>-6.064264404887064</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.9247930099454303</v>
       </c>
       <c r="E22">
-        <v>-21.23253138884237</v>
+        <v>-25.05957856869815</v>
       </c>
       <c r="F22">
-        <v>0.07029925239107229</v>
+        <v>-1.887316817987581</v>
       </c>
       <c r="G22">
-        <v>-4.605038319831524</v>
+        <v>-6.241319881567185</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.515105596700594</v>
       </c>
       <c r="E23">
-        <v>-22.52682155326664</v>
+        <v>-26.79704960717223</v>
       </c>
       <c r="F23">
-        <v>0.2189414991494156</v>
+        <v>-1.587445333071952</v>
       </c>
       <c r="G23">
-        <v>-4.404929968411873</v>
+        <v>-5.962416647643144</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.138205864631039</v>
       </c>
       <c r="E24">
-        <v>-21.62044547979268</v>
+        <v>-25.6863189236714</v>
       </c>
       <c r="F24">
-        <v>0.5783999364506218</v>
+        <v>-1.324375726760496</v>
       </c>
       <c r="G24">
-        <v>-3.305702065769535</v>
+        <v>-6.090481502071024</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.755666849996557</v>
       </c>
       <c r="E25">
-        <v>-23.0528133079222</v>
+        <v>-26.22232822404245</v>
       </c>
       <c r="F25">
-        <v>0.5797601157260186</v>
+        <v>-0.8489383977607335</v>
       </c>
       <c r="G25">
-        <v>-4.616431609227143</v>
+        <v>-6.635620637163025</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.32970997682968</v>
       </c>
       <c r="E26">
-        <v>-21.68901084555428</v>
+        <v>-26.65628481573981</v>
       </c>
       <c r="F26">
-        <v>0.811464418697874</v>
+        <v>-0.9768714594490892</v>
       </c>
       <c r="G26">
-        <v>-4.767922674871082</v>
+        <v>-6.556259223082363</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.835238070662742</v>
       </c>
       <c r="E27">
-        <v>-23.10285535117506</v>
+        <v>-26.99411117811269</v>
       </c>
       <c r="F27">
-        <v>0.9247502879699288</v>
+        <v>-0.676891458403693</v>
       </c>
       <c r="G27">
-        <v>-4.595279356549943</v>
+        <v>-7.000532240896702</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.25008824325841</v>
       </c>
       <c r="E28">
-        <v>-21.59968357637986</v>
+        <v>-26.48632294869385</v>
       </c>
       <c r="F28">
-        <v>0.7653359515055806</v>
+        <v>-0.8520480889908428</v>
       </c>
       <c r="G28">
-        <v>-3.976237874317298</v>
+        <v>-6.890494577870459</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.558823802843219</v>
       </c>
       <c r="E29">
-        <v>-22.8686765306246</v>
+        <v>-26.00517756992379</v>
       </c>
       <c r="F29">
-        <v>0.5162823216494925</v>
+        <v>-0.8505793935856794</v>
       </c>
       <c r="G29">
-        <v>-5.226996003772443</v>
+        <v>-7.089083475938082</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.753846833017289</v>
       </c>
       <c r="E30">
-        <v>-21.9967015065542</v>
+        <v>-27.02373188128137</v>
       </c>
       <c r="F30">
-        <v>0.5279291673328536</v>
+        <v>-0.7819814605924494</v>
       </c>
       <c r="G30">
-        <v>-4.791364550554689</v>
+        <v>-7.323977388289727</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.830732558887645</v>
       </c>
       <c r="E31">
-        <v>-23.1825180975966</v>
+        <v>-26.91365516832811</v>
       </c>
       <c r="F31">
-        <v>0.1294214906636786</v>
+        <v>-0.8393914634434692</v>
       </c>
       <c r="G31">
-        <v>-4.950053439036327</v>
+        <v>-6.772188686724161</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.792118887420187</v>
       </c>
       <c r="E32">
-        <v>-22.46223496395423</v>
+        <v>-26.01625418452711</v>
       </c>
       <c r="F32">
-        <v>0.6433729336892011</v>
+        <v>-1.071280492346149</v>
       </c>
       <c r="G32">
-        <v>-4.14140663087408</v>
+        <v>-7.184918688388668</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.646268020091365</v>
       </c>
       <c r="E33">
-        <v>-22.22991262886597</v>
+        <v>-25.45747282646203</v>
       </c>
       <c r="F33">
-        <v>0.5334278701526367</v>
+        <v>-0.932316890322115</v>
       </c>
       <c r="G33">
-        <v>-4.307786772921139</v>
+        <v>-6.674826188687772</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.403747081351321</v>
       </c>
       <c r="E34">
-        <v>-21.90613658040499</v>
+        <v>-26.54100828220787</v>
       </c>
       <c r="F34">
-        <v>-0.1776700445347513</v>
+        <v>-1.480961188544283</v>
       </c>
       <c r="G34">
-        <v>-3.689606836403562</v>
+        <v>-6.779135878081113</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.079037804247665</v>
       </c>
       <c r="E35">
-        <v>-22.72946088701635</v>
+        <v>-25.97384989690061</v>
       </c>
       <c r="F35">
-        <v>0.9161634314725091</v>
+        <v>-1.25850726435949</v>
       </c>
       <c r="G35">
-        <v>-3.973535753665496</v>
+        <v>-6.306040239980883</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.690785589517756</v>
       </c>
       <c r="E36">
-        <v>-20.7444252278919</v>
+        <v>-24.78304945226842</v>
       </c>
       <c r="F36">
-        <v>0.1747075082073248</v>
+        <v>-1.192818557684892</v>
       </c>
       <c r="G36">
-        <v>-4.206022559504135</v>
+        <v>-6.000818089833829</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.256340268051011</v>
       </c>
       <c r="E37">
-        <v>-20.77350186037702</v>
+        <v>-24.61204512917993</v>
       </c>
       <c r="F37">
-        <v>0.7521152077569006</v>
+        <v>-1.43453368071958</v>
       </c>
       <c r="G37">
-        <v>-2.710585446969853</v>
+        <v>-5.606183158930327</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.797702623381839</v>
       </c>
       <c r="E38">
-        <v>-20.33961587327218</v>
+        <v>-24.51265878217678</v>
       </c>
       <c r="F38">
-        <v>-0.09930731659732088</v>
+        <v>-1.456111823195104</v>
       </c>
       <c r="G38">
-        <v>-3.348677532483851</v>
+        <v>-5.690601585283975</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.338137293950231</v>
       </c>
       <c r="E39">
-        <v>-21.00474851373215</v>
+        <v>-24.32730511396101</v>
       </c>
       <c r="F39">
-        <v>0.03905820416189174</v>
+        <v>-1.493827391044565</v>
       </c>
       <c r="G39">
-        <v>-3.252066928889704</v>
+        <v>-4.921465785763637</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.897832339997548</v>
       </c>
       <c r="E40">
-        <v>-20.04329255166832</v>
+        <v>-23.22356013190855</v>
       </c>
       <c r="F40">
-        <v>0.06060072683909568</v>
+        <v>-1.339148002654619</v>
       </c>
       <c r="G40">
-        <v>-2.365740026163472</v>
+        <v>-4.850787708193018</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.503131285077197</v>
       </c>
       <c r="E41">
-        <v>-18.60815453158514</v>
+        <v>-23.47776573746733</v>
       </c>
       <c r="F41">
-        <v>0.1932198629250881</v>
+        <v>-1.41789260796474</v>
       </c>
       <c r="G41">
-        <v>-2.565114758353021</v>
+        <v>-4.752192938709625</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.173619093262183</v>
       </c>
       <c r="E42">
-        <v>-19.12225564221772</v>
+        <v>-22.89054734146115</v>
       </c>
       <c r="F42">
-        <v>-0.1804815234998528</v>
+        <v>-1.357826859220345</v>
       </c>
       <c r="G42">
-        <v>-2.3642336265344</v>
+        <v>-5.233013770054958</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.9240680586501273</v>
       </c>
       <c r="E43">
-        <v>-18.76706885650706</v>
+        <v>-21.07604253933416</v>
       </c>
       <c r="F43">
-        <v>-0.04008981607339263</v>
+        <v>-1.491615650079091</v>
       </c>
       <c r="G43">
-        <v>-2.632354485297144</v>
+        <v>-4.881563165433062</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.7715560206191566</v>
       </c>
       <c r="E44">
-        <v>-17.59078388545514</v>
+        <v>-21.92686525812721</v>
       </c>
       <c r="F44">
-        <v>0.01517057336736239</v>
+        <v>-1.379738005391795</v>
       </c>
       <c r="G44">
-        <v>-1.473606827466605</v>
+        <v>-4.095679439360731</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7182082293655324</v>
       </c>
       <c r="E45">
-        <v>-16.18541608414833</v>
+        <v>-21.58651789648016</v>
       </c>
       <c r="F45">
-        <v>-0.2330157558179947</v>
+        <v>-1.575454714916429</v>
       </c>
       <c r="G45">
-        <v>-3.167097635427331</v>
+        <v>-4.056528713472396</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7665477827936634</v>
       </c>
       <c r="E46">
-        <v>-16.24470732902159</v>
+        <v>-21.3330017240013</v>
       </c>
       <c r="F46">
-        <v>0.05970360494186382</v>
+        <v>-1.335668859562861</v>
       </c>
       <c r="G46">
-        <v>-1.953850684257303</v>
+        <v>-3.412988003996745</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.9138240841479899</v>
       </c>
       <c r="E47">
-        <v>-15.90900741084702</v>
+        <v>-19.86592135561887</v>
       </c>
       <c r="F47">
-        <v>-0.2457759272907183</v>
+        <v>-1.375587884703769</v>
       </c>
       <c r="G47">
-        <v>-1.990904982238974</v>
+        <v>-3.646842840001126</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.146878374416576</v>
       </c>
       <c r="E48">
-        <v>-16.66416921319529</v>
+        <v>-21.03819847774232</v>
       </c>
       <c r="F48">
-        <v>-0.4835571335295107</v>
+        <v>-1.649712882372988</v>
       </c>
       <c r="G48">
-        <v>-1.569107864609529</v>
+        <v>-4.30483402078859</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.455540677936233</v>
       </c>
       <c r="E49">
-        <v>-16.3726594635169</v>
+        <v>-19.35123048897816</v>
       </c>
       <c r="F49">
-        <v>0.2270015139786548</v>
+        <v>-1.191417788406758</v>
       </c>
       <c r="G49">
-        <v>-2.222404926622171</v>
+        <v>-3.837662162165596</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.821071224465916</v>
       </c>
       <c r="E50">
-        <v>-15.07377584736738</v>
+        <v>-18.93173953232518</v>
       </c>
       <c r="F50">
-        <v>-0.52500035469157</v>
+        <v>-1.642892933545739</v>
       </c>
       <c r="G50">
-        <v>-2.228960506290457</v>
+        <v>-4.088379797483978</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.222809685088359</v>
       </c>
       <c r="E51">
-        <v>-13.57852009335731</v>
+        <v>-18.75769090533559</v>
       </c>
       <c r="F51">
-        <v>-0.07312096626002292</v>
+        <v>-1.554780321277359</v>
       </c>
       <c r="G51">
-        <v>-1.157586637690706</v>
+        <v>-3.826169664475516</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.643689505974499</v>
       </c>
       <c r="E52">
-        <v>-14.53109648960866</v>
+        <v>-18.92099932783918</v>
       </c>
       <c r="F52">
-        <v>0.002098935751186195</v>
+        <v>-1.713566755250385</v>
       </c>
       <c r="G52">
-        <v>-1.952662795468346</v>
+        <v>-3.677714894791041</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.059640650576983</v>
       </c>
       <c r="E53">
-        <v>-13.60550766054604</v>
+        <v>-18.07452502130322</v>
       </c>
       <c r="F53">
-        <v>-0.09409191542929519</v>
+        <v>-1.826773101251771</v>
       </c>
       <c r="G53">
-        <v>-1.844760721517634</v>
+        <v>-3.973295565163114</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.454565979251072</v>
       </c>
       <c r="E54">
-        <v>-13.8971129340849</v>
+        <v>-19.30103062369496</v>
       </c>
       <c r="F54">
-        <v>0.4764718126383511</v>
+        <v>-1.567879295017827</v>
       </c>
       <c r="G54">
-        <v>-1.664877808445338</v>
+        <v>-4.048135169611967</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.814064312996408</v>
       </c>
       <c r="E55">
-        <v>-12.73992442870455</v>
+        <v>-17.82528665648893</v>
       </c>
       <c r="F55">
-        <v>-0.6967905001537427</v>
+        <v>-1.597473548850242</v>
       </c>
       <c r="G55">
-        <v>-2.266826745839964</v>
+        <v>-3.815470833141133</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.122185873260989</v>
       </c>
       <c r="E56">
-        <v>-12.86251061416819</v>
+        <v>-17.789282467514</v>
       </c>
       <c r="F56">
-        <v>-1.154951398600718</v>
+        <v>-1.684438043898343</v>
       </c>
       <c r="G56">
-        <v>-2.205563013264899</v>
+        <v>-4.78759202462053</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.372386876825817</v>
       </c>
       <c r="E57">
-        <v>-12.72349432470353</v>
+        <v>-16.73584948745051</v>
       </c>
       <c r="F57">
-        <v>-0.4063118732184569</v>
+        <v>-1.849565630339799</v>
       </c>
       <c r="G57">
-        <v>-2.70668499455073</v>
+        <v>-4.335494605266624</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.558487225211161</v>
       </c>
       <c r="E58">
-        <v>-11.84094937781144</v>
+        <v>-15.97337387995921</v>
       </c>
       <c r="F58">
-        <v>-0.815585841021817</v>
+        <v>-1.707907349154459</v>
       </c>
       <c r="G58">
-        <v>-2.628135522037904</v>
+        <v>-4.828836567670938</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.677757260315819</v>
       </c>
       <c r="E59">
-        <v>-12.8434764466665</v>
+        <v>-15.93402635586779</v>
       </c>
       <c r="F59">
-        <v>-0.8170329988745078</v>
+        <v>-2.021813034608317</v>
       </c>
       <c r="G59">
-        <v>-2.384850676570422</v>
+        <v>-3.975485979875058</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.73727808410413</v>
       </c>
       <c r="E60">
-        <v>-11.77043200272717</v>
+        <v>-15.83250525824368</v>
       </c>
       <c r="F60">
-        <v>0.01484336824325659</v>
+        <v>-1.793432970023896</v>
       </c>
       <c r="G60">
-        <v>-2.822863128855271</v>
+        <v>-4.63340405981397</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.743839221939175</v>
       </c>
       <c r="E61">
-        <v>-11.39047961788656</v>
+        <v>-15.29035335832321</v>
       </c>
       <c r="F61">
-        <v>-0.8611775261370962</v>
+        <v>-1.963011374520594</v>
       </c>
       <c r="G61">
-        <v>-3.317413866005269</v>
+        <v>-4.690683796142996</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.708580034370533</v>
       </c>
       <c r="E62">
-        <v>-11.13459196174122</v>
+        <v>-14.88174381534128</v>
       </c>
       <c r="F62">
-        <v>-0.06310434762537129</v>
+        <v>-2.036162843127013</v>
       </c>
       <c r="G62">
-        <v>-3.166938380007273</v>
+        <v>-5.306537559229891</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.647896590407275</v>
       </c>
       <c r="E63">
-        <v>-11.05085491501003</v>
+        <v>-14.58422436887586</v>
       </c>
       <c r="F63">
-        <v>-1.154079956092973</v>
+        <v>-1.841123738137869</v>
       </c>
       <c r="G63">
-        <v>-2.843033741566212</v>
+        <v>-5.521939652464284</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.570469302652962</v>
       </c>
       <c r="E64">
-        <v>-11.33111776842079</v>
+        <v>-14.23998544821745</v>
       </c>
       <c r="F64">
-        <v>-0.9638321281616221</v>
+        <v>-2.068204094267298</v>
       </c>
       <c r="G64">
-        <v>-3.275743771586511</v>
+        <v>-5.308767135110702</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.488418515383788</v>
       </c>
       <c r="E65">
-        <v>-11.1538919347677</v>
+        <v>-14.02706691643879</v>
       </c>
       <c r="F65">
-        <v>-0.7198340245648194</v>
+        <v>-2.204180603436837</v>
       </c>
       <c r="G65">
-        <v>-3.64295805204955</v>
+        <v>-5.367955325735831</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.412129300475041</v>
       </c>
       <c r="E66">
-        <v>-9.369726341368583</v>
+        <v>-14.84124169850155</v>
       </c>
       <c r="F66">
-        <v>-0.5041180408343973</v>
+        <v>-2.414604976198175</v>
       </c>
       <c r="G66">
-        <v>-2.810866757459106</v>
+        <v>-5.386859727320083</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.342181262228684</v>
       </c>
       <c r="E67">
-        <v>-10.62546639827579</v>
+        <v>-13.4387105405296</v>
       </c>
       <c r="F67">
-        <v>-0.9152757161117235</v>
+        <v>-2.709169939531471</v>
       </c>
       <c r="G67">
-        <v>-3.531351331524048</v>
+        <v>-5.469690820962334</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.282156734031815</v>
       </c>
       <c r="E68">
-        <v>-11.1223607543896</v>
+        <v>-14.79949361826437</v>
       </c>
       <c r="F68">
-        <v>-0.2617866124520271</v>
+        <v>-2.628773569620168</v>
       </c>
       <c r="G68">
-        <v>-3.774348995086508</v>
+        <v>-5.943245950110599</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.230045807594591</v>
       </c>
       <c r="E69">
-        <v>-8.548221141317498</v>
+        <v>-13.79883549450549</v>
       </c>
       <c r="F69">
-        <v>-1.303118162469855</v>
+        <v>-2.643969141257122</v>
       </c>
       <c r="G69">
-        <v>-4.273468535270955</v>
+        <v>-5.867516081756176</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.177566628811987</v>
       </c>
       <c r="E70">
-        <v>-10.47022766537635</v>
+        <v>-14.54041629582157</v>
       </c>
       <c r="F70">
-        <v>-1.576043684139819</v>
+        <v>-2.482014201968388</v>
       </c>
       <c r="G70">
-        <v>-3.843207383677121</v>
+        <v>-5.609300387972117</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.122522409000332</v>
       </c>
       <c r="E71">
-        <v>-10.11520700811868</v>
+        <v>-14.55313758210952</v>
       </c>
       <c r="F71">
-        <v>-1.869327991468387</v>
+        <v>-2.889831899877627</v>
       </c>
       <c r="G71">
-        <v>-4.135746536600547</v>
+        <v>-5.65571942680211</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.057362026677013</v>
       </c>
       <c r="E72">
-        <v>-11.32137433465274</v>
+        <v>-14.46828747474327</v>
       </c>
       <c r="F72">
-        <v>-1.569200541025292</v>
+        <v>-3.063428714645305</v>
       </c>
       <c r="G72">
-        <v>-3.575300605970849</v>
+        <v>-5.827164413355929</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.97423814861452</v>
       </c>
       <c r="E73">
-        <v>-10.51001542986821</v>
+        <v>-14.83359563645254</v>
       </c>
       <c r="F73">
-        <v>-2.239223858044867</v>
+        <v>-3.019867358034288</v>
       </c>
       <c r="G73">
-        <v>-3.067876287242071</v>
+        <v>-5.480708163136832</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.872481795781411</v>
       </c>
       <c r="E74">
-        <v>-10.89067801384537</v>
+        <v>-14.86347799193468</v>
       </c>
       <c r="F74">
-        <v>-1.407712800951737</v>
+        <v>-2.777732252726381</v>
       </c>
       <c r="G74">
-        <v>-3.499502858257057</v>
+        <v>-5.946903603282749</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.744333624927209</v>
       </c>
       <c r="E75">
-        <v>-12.17005399640218</v>
+        <v>-14.74632420688392</v>
       </c>
       <c r="F75">
-        <v>-1.487050517322263</v>
+        <v>-3.336494230406343</v>
       </c>
       <c r="G75">
-        <v>-2.774089198404093</v>
+        <v>-5.930210502367171</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.585750319827266</v>
       </c>
       <c r="E76">
-        <v>-12.55496531556464</v>
+        <v>-14.62272463785702</v>
       </c>
       <c r="F76">
-        <v>-1.543608958483204</v>
+        <v>-3.102035605820179</v>
       </c>
       <c r="G76">
-        <v>-3.460944771390905</v>
+        <v>-5.627110887572691</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.39718109330721</v>
       </c>
       <c r="E77">
-        <v>-11.24714398864408</v>
+        <v>-14.96590033641628</v>
       </c>
       <c r="F77">
-        <v>-2.045493573552147</v>
+        <v>-3.409084065913663</v>
       </c>
       <c r="G77">
-        <v>-3.40322120848139</v>
+        <v>-5.766255742045256</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.176722726643302</v>
       </c>
       <c r="E78">
-        <v>-13.59675684428463</v>
+        <v>-16.07860794850772</v>
       </c>
       <c r="F78">
-        <v>-2.590006803536554</v>
+        <v>-3.395865807267191</v>
       </c>
       <c r="G78">
-        <v>-2.36587578488221</v>
+        <v>-5.029775135870563</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.930509676353861</v>
       </c>
       <c r="E79">
-        <v>-11.92832048445186</v>
+        <v>-15.46230876680509</v>
       </c>
       <c r="F79">
-        <v>-1.841941336764432</v>
+        <v>-3.628926976044832</v>
       </c>
       <c r="G79">
-        <v>-2.594315936604623</v>
+        <v>-4.663336246551084</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.666501838937953</v>
       </c>
       <c r="E80">
-        <v>-13.19994657467653</v>
+        <v>-16.367405651191</v>
       </c>
       <c r="F80">
-        <v>-1.971732426537267</v>
+        <v>-3.600065827363895</v>
       </c>
       <c r="G80">
-        <v>-1.427853528507345</v>
+        <v>-5.030339056702243</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.391977081986317</v>
       </c>
       <c r="E81">
-        <v>-13.86127902677428</v>
+        <v>-17.21742680019835</v>
       </c>
       <c r="F81">
-        <v>-2.15031352796759</v>
+        <v>-4.06884059734294</v>
       </c>
       <c r="G81">
-        <v>-2.247783974792383</v>
+        <v>-4.672197113693323</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.121984260820066</v>
       </c>
       <c r="E82">
-        <v>-14.61548143730652</v>
+        <v>-17.97977365813858</v>
       </c>
       <c r="F82">
-        <v>-2.517719322131255</v>
+        <v>-4.030693450076621</v>
       </c>
       <c r="G82">
-        <v>-2.254621514876509</v>
+        <v>-4.562083739073937</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-1.867130282864627</v>
       </c>
       <c r="E83">
-        <v>-14.99571624051722</v>
+        <v>-18.83580865714429</v>
       </c>
       <c r="F83">
-        <v>-2.366269738244824</v>
+        <v>-3.711887971435203</v>
       </c>
       <c r="G83">
-        <v>-1.539752652427051</v>
+        <v>-3.892164066249677</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.638159289610916</v>
       </c>
       <c r="E84">
-        <v>-18.2293359734362</v>
+        <v>-19.71834114440241</v>
       </c>
       <c r="F84">
-        <v>-3.004337954334005</v>
+        <v>-3.753302199738164</v>
       </c>
       <c r="G84">
-        <v>-1.945162126258078</v>
+        <v>-3.895479711880391</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.450658610622918</v>
       </c>
       <c r="E85">
-        <v>-18.49552774687844</v>
+        <v>-20.53573881845324</v>
       </c>
       <c r="F85">
-        <v>-2.434306038138956</v>
+        <v>-3.935148725470323</v>
       </c>
       <c r="G85">
-        <v>-1.937329892484738</v>
+        <v>-4.268301871725142</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.31164415378444</v>
       </c>
       <c r="E86">
-        <v>-19.35790885278849</v>
+        <v>-21.87499580189142</v>
       </c>
       <c r="F86">
-        <v>-2.665969751108074</v>
+        <v>-3.696983156756631</v>
       </c>
       <c r="G86">
-        <v>-1.961698582498189</v>
+        <v>-3.75608422592708</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-1.232634834720175</v>
       </c>
       <c r="E87">
-        <v>-20.60166274181224</v>
+        <v>-22.60308281961314</v>
       </c>
       <c r="F87">
-        <v>-3.33450200680261</v>
+        <v>-3.786541270142897</v>
       </c>
       <c r="G87">
-        <v>-1.210185308967866</v>
+        <v>-3.820851577743418</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-1.222284288602091</v>
       </c>
       <c r="E88">
-        <v>-21.73675200973318</v>
+        <v>-23.48805324191893</v>
       </c>
       <c r="F88">
-        <v>-2.700642725487053</v>
+        <v>-4.055292648470155</v>
       </c>
       <c r="G88">
-        <v>-1.798046668548844</v>
+        <v>-3.703681360494254</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.282450139807636</v>
       </c>
       <c r="E89">
-        <v>-23.94331165450134</v>
+        <v>-24.90629599833271</v>
       </c>
       <c r="F89">
-        <v>-3.370241918396395</v>
+        <v>-4.282093016417437</v>
       </c>
       <c r="G89">
-        <v>-1.467479409911262</v>
+        <v>-3.353139294990064</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.420973354997075</v>
       </c>
       <c r="E90">
-        <v>-24.41424013341232</v>
+        <v>-26.37623792931795</v>
       </c>
       <c r="F90">
-        <v>-3.159152366610607</v>
+        <v>-4.253242636512736</v>
       </c>
       <c r="G90">
-        <v>-0.7327062306991567</v>
+        <v>-3.74963568678703</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.636482575857612</v>
       </c>
       <c r="E91">
-        <v>-26.25750177075243</v>
+        <v>-27.69443397812793</v>
       </c>
       <c r="F91">
-        <v>-3.269668175287701</v>
+        <v>-4.442170875171428</v>
       </c>
       <c r="G91">
-        <v>-1.229324677565317</v>
+        <v>-2.884484533439318</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.927915476493716</v>
       </c>
       <c r="E92">
-        <v>-26.68874216224335</v>
+        <v>-30.22905370883863</v>
       </c>
       <c r="F92">
-        <v>-3.356151388874775</v>
+        <v>-4.744580477809235</v>
       </c>
       <c r="G92">
-        <v>-0.9613552419888582</v>
+        <v>-3.274976212676723</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.298785465229255</v>
       </c>
       <c r="E93">
-        <v>-30.16489697689834</v>
+        <v>-30.7072648438077</v>
       </c>
       <c r="F93">
-        <v>-3.175776043649988</v>
+        <v>-4.9092963656515</v>
       </c>
       <c r="G93">
-        <v>-0.7888032997284079</v>
+        <v>-3.05031119763306</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.739501992839019</v>
       </c>
       <c r="E94">
-        <v>-31.37437441285828</v>
+        <v>-33.81057757141019</v>
       </c>
       <c r="F94">
-        <v>-3.645015527742004</v>
+        <v>-4.817851231321656</v>
       </c>
       <c r="G94">
-        <v>-1.681724943291792</v>
+        <v>-3.472562584821359</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.248454833469189</v>
       </c>
       <c r="E95">
-        <v>-33.27020947575373</v>
+        <v>-35.18508285936219</v>
       </c>
       <c r="F95">
-        <v>-3.656811479557869</v>
+        <v>-4.562023212845474</v>
       </c>
       <c r="G95">
-        <v>-1.912397281639606</v>
+        <v>-3.428012839118602</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.822725871259571</v>
       </c>
       <c r="E96">
-        <v>-36.66799942252619</v>
+        <v>-37.427137924718</v>
       </c>
       <c r="F96">
-        <v>-4.11654793280497</v>
+        <v>-4.861701688156251</v>
       </c>
       <c r="G96">
-        <v>-1.055746712680559</v>
+        <v>-3.311842537047834</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.439487111073641</v>
       </c>
       <c r="E97">
-        <v>-37.94107498350324</v>
+        <v>-39.83747695974452</v>
       </c>
       <c r="F97">
-        <v>-4.130215994951161</v>
+        <v>-4.647390615540977</v>
       </c>
       <c r="G97">
-        <v>-1.576898326469411</v>
+        <v>-3.865435263125859</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.100143876116285</v>
       </c>
       <c r="E98">
-        <v>-39.26909960691343</v>
+        <v>-41.17115202716214</v>
       </c>
       <c r="F98">
-        <v>-4.828215764265484</v>
+        <v>-5.177825741514806</v>
       </c>
       <c r="G98">
-        <v>-3.039095438869638</v>
+        <v>-4.427144794137656</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-5.768488224627103</v>
       </c>
       <c r="E99">
-        <v>-43.46615430709252</v>
+        <v>-43.40863025363798</v>
       </c>
       <c r="F99">
-        <v>-3.973329007432755</v>
+        <v>-4.601411254481188</v>
       </c>
       <c r="G99">
-        <v>-3.003414392542893</v>
+        <v>-5.139601328584925</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.449649055647856</v>
       </c>
       <c r="E100">
-        <v>-44.60972027932743</v>
+        <v>-46.0915673905753</v>
       </c>
       <c r="F100">
-        <v>-3.957552750246438</v>
+        <v>-4.802098168422618</v>
       </c>
       <c r="G100">
-        <v>-2.773945607451581</v>
+        <v>-5.305234797678925</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.086870283176546</v>
       </c>
       <c r="E101">
-        <v>-48.49151612916994</v>
+        <v>-49.08057855100434</v>
       </c>
       <c r="F101">
-        <v>-4.327654880306215</v>
+        <v>-4.77096149448619</v>
       </c>
       <c r="G101">
-        <v>-2.983337766637231</v>
+        <v>-5.680216043300526</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.728614813047428</v>
       </c>
       <c r="E102">
-        <v>-48.92309189247534</v>
+        <v>-50.66989312019064</v>
       </c>
       <c r="F102">
-        <v>-4.493861829473519</v>
+        <v>-4.521045534163788</v>
       </c>
       <c r="G102">
-        <v>-4.790503004839621</v>
+        <v>-6.670651608086582</v>
       </c>
     </row>
   </sheetData>
